--- a/series_historicas_brasil_2010_2025.xlsx
+++ b/series_historicas_brasil_2010_2025.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Series_Historicas_2016_2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veiculos_Vendas_Mensais" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario_e_Fontes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orcamento_Federal_Governos" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Veiculos_Vendas_Mensais" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario_e_Fontes" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1825,1793 +1826,1339 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Ano</t>
+          <t>governo</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Veiculos_Novos_Vendidos_Unidades</t>
+          <t>despesa_total_uniao_bi</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Veiculos_Novos_Milhares</t>
+          <t>saude_bi</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>educacao_bi</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fundeb_compl_uniao_bi</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>investimento_total_bi</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>obras_pac_bi</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>farmacia_popular_bi</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>conab_orcamento_executado_bi</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pnae_compras_agricultura_familiar_bi</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>deflator_ipca_2026</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>despesa_total_uniao_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>saude_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>educacao_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>fundeb_compl_uniao_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>investimento_total_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>obras_pac_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>farmacia_popular_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>conab_orcamento_executado_real_2026_bi</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>pnae_compras_agricultura_familiar_real_2026_bi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>42370</v>
-      </c>
-      <c r="B2" t="n">
+      <c r="A2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Lula 2 (2010)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>707.27</v>
+      </c>
+      <c r="D2" t="n">
+        <v>50.48</v>
+      </c>
+      <c r="E2" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="G2" t="n">
+        <v>44.74</v>
+      </c>
+      <c r="H2" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="M2" t="n">
+        <v>2.437643308406219</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1724.07</v>
+      </c>
+      <c r="O2" t="n">
+        <v>123.05</v>
+      </c>
+      <c r="P2" t="n">
+        <v>42.81</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="R2" t="n">
+        <v>109.06</v>
+      </c>
+      <c r="S2" t="n">
+        <v>53.82</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U2" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dilma (2011-2015)</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>733.34</v>
+      </c>
+      <c r="D3" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.13</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="G3" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="H3" t="n">
+        <v>28.02</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.285940019559019</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1676.37</v>
+      </c>
+      <c r="O3" t="n">
+        <v>133.22</v>
+      </c>
+      <c r="P3" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="R3" t="n">
+        <v>120.31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U3" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Dilma (2011-2015)</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>815.91</v>
+      </c>
+      <c r="D4" t="n">
+        <v>66.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="G4" t="n">
+        <v>59.45</v>
+      </c>
+      <c r="H4" t="n">
+        <v>39.31</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.16874879821238</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1769.5</v>
+      </c>
+      <c r="O4" t="n">
+        <v>143.44</v>
+      </c>
+      <c r="P4" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>22.49</v>
+      </c>
+      <c r="R4" t="n">
+        <v>128.93</v>
+      </c>
+      <c r="S4" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Dilma (2011-2015)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>924.9299999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>71.01000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>63.22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.042055218042961</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1888.76</v>
+      </c>
+      <c r="O5" t="n">
+        <v>145.01</v>
+      </c>
+      <c r="P5" t="n">
+        <v>63.36</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>18.93</v>
+      </c>
+      <c r="R5" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Dilma (2011-2015)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1046.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>84.02</v>
+      </c>
+      <c r="E6" t="n">
+        <v>37.73</v>
+      </c>
+      <c r="F6" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="G6" t="n">
+        <v>77.54000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.920503023884025</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2009.81</v>
+      </c>
+      <c r="O6" t="n">
+        <v>161.36</v>
+      </c>
+      <c r="P6" t="n">
+        <v>72.45999999999999</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="R6" t="n">
+        <v>148.92</v>
+      </c>
+      <c r="S6" t="n">
+        <v>110.81</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9.51</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Dilma (2011-2015)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1164.92</v>
+      </c>
+      <c r="D7" t="n">
+        <v>87.67</v>
+      </c>
+      <c r="E7" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="F7" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="G7" t="n">
+        <v>55.53</v>
+      </c>
+      <c r="H7" t="n">
+        <v>47.26</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.761442152482485</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2051.94</v>
+      </c>
+      <c r="O7" t="n">
+        <v>154.43</v>
+      </c>
+      <c r="P7" t="n">
+        <v>59.31</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23.41</v>
+      </c>
+      <c r="R7" t="n">
+        <v>97.81</v>
+      </c>
+      <c r="S7" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="U7" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>2016</v>
       </c>
-      <c r="C2" t="n">
-        <v>147444</v>
-      </c>
-      <c r="D2" t="n">
-        <v>147.444</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>42401</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C3" t="n">
-        <v>137507</v>
-      </c>
-      <c r="D3" t="n">
-        <v>137.507</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>42430</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C4" t="n">
-        <v>193037</v>
-      </c>
-      <c r="D4" t="n">
-        <v>193.037</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>42461</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C5" t="n">
-        <v>164516</v>
-      </c>
-      <c r="D5" t="n">
-        <v>164.516</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>42491</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C6" t="n">
-        <v>172072</v>
-      </c>
-      <c r="D6" t="n">
-        <v>172.072</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>42522</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C7" t="n">
-        <v>178856</v>
-      </c>
-      <c r="D7" t="n">
-        <v>178.856</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>42552</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2016</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Dilma / Temer (2016)</t>
+        </is>
       </c>
       <c r="C8" t="n">
-        <v>185053</v>
+        <v>1250.43</v>
       </c>
       <c r="D8" t="n">
-        <v>185.053</v>
+        <v>99.42</v>
+      </c>
+      <c r="E8" t="n">
+        <v>34.81</v>
+      </c>
+      <c r="F8" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>64.81</v>
+      </c>
+      <c r="H8" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.619872566573324</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2025.54</v>
+      </c>
+      <c r="O8" t="n">
+        <v>161.05</v>
+      </c>
+      <c r="P8" t="n">
+        <v>56.39</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="R8" t="n">
+        <v>104.98</v>
+      </c>
+      <c r="S8" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.49</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>42583</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2016</v>
+      <c r="A9" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Temer (2017-2018)</t>
+        </is>
       </c>
       <c r="C9" t="n">
-        <v>174522</v>
+        <v>1279.58</v>
       </c>
       <c r="D9" t="n">
-        <v>174.522</v>
+        <v>97.86</v>
+      </c>
+      <c r="E9" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="F9" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>45.69</v>
+      </c>
+      <c r="H9" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.565906616507605</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2003.7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>153.24</v>
+      </c>
+      <c r="P9" t="n">
+        <v>46.93</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="R9" t="n">
+        <v>71.55</v>
+      </c>
+      <c r="S9" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="U9" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.53</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>42614</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2016</v>
+      <c r="A10" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Temer (2017-2018)</t>
+        </is>
       </c>
       <c r="C10" t="n">
-        <v>165115</v>
+        <v>1352.5</v>
       </c>
       <c r="D10" t="n">
-        <v>165.115</v>
+        <v>111.18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="G10" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.510549851243476</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2043.02</v>
+      </c>
+      <c r="O10" t="n">
+        <v>167.94</v>
+      </c>
+      <c r="P10" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="R10" t="n">
+        <v>80.26000000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>41.69</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4.23</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.59</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>42644</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2016</v>
+      <c r="A11" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bolsonaro (2019-2022)</t>
+        </is>
       </c>
       <c r="C11" t="n">
-        <v>171281</v>
+        <v>1442.34</v>
       </c>
       <c r="D11" t="n">
-        <v>171.281</v>
+        <v>115.38</v>
+      </c>
+      <c r="E11" t="n">
+        <v>27.57</v>
+      </c>
+      <c r="F11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>56.59</v>
+      </c>
+      <c r="H11" t="n">
+        <v>27.08</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.45618970323442</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2100.32</v>
+      </c>
+      <c r="O11" t="n">
+        <v>168.02</v>
+      </c>
+      <c r="P11" t="n">
+        <v>40.15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>22.72</v>
+      </c>
+      <c r="R11" t="n">
+        <v>82.41</v>
+      </c>
+      <c r="S11" t="n">
+        <v>39.43</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.63</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>42675</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2016</v>
+      <c r="A12" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bolsonaro (2019-2022)</t>
+        </is>
       </c>
       <c r="C12" t="n">
-        <v>212126</v>
+        <v>1947.55</v>
       </c>
       <c r="D12" t="n">
-        <v>212.126</v>
+        <v>112.41</v>
+      </c>
+      <c r="E12" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15</v>
+      </c>
+      <c r="G12" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.410878071133771</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2747.76</v>
+      </c>
+      <c r="O12" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>36.88</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>21.16</v>
+      </c>
+      <c r="R12" t="n">
+        <v>148</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>42705</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2016</v>
+      <c r="A13" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bolsonaro (2019-2022)</t>
+        </is>
       </c>
       <c r="C13" t="n">
-        <v>196068</v>
+        <v>1614.17</v>
       </c>
       <c r="D13" t="n">
-        <v>196.068</v>
+        <v>123.17</v>
+      </c>
+      <c r="E13" t="n">
+        <v>26.83</v>
+      </c>
+      <c r="F13" t="n">
+        <v>22.03</v>
+      </c>
+      <c r="G13" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.302730905071444</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2102.83</v>
+      </c>
+      <c r="O13" t="n">
+        <v>160.46</v>
+      </c>
+      <c r="P13" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="R13" t="n">
+        <v>74.03</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="U13" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.98</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>42736</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2017</v>
+      <c r="A14" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bolsonaro (2019-2022)</t>
+        </is>
       </c>
       <c r="C14" t="n">
-        <v>173825</v>
+        <v>1809.69</v>
       </c>
       <c r="D14" t="n">
-        <v>173.825</v>
+        <v>137.7</v>
+      </c>
+      <c r="E14" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="F14" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="G14" t="n">
+        <v>45.05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.192104377360772</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2157.34</v>
+      </c>
+      <c r="O14" t="n">
+        <v>164.15</v>
+      </c>
+      <c r="P14" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>53.7</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.41</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>42767</v>
-      </c>
-      <c r="B15" t="n">
-        <v>2017</v>
+      <c r="A15" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lula 3 (2023-2026)</t>
+        </is>
       </c>
       <c r="C15" t="n">
-        <v>195091</v>
+        <v>2129.92</v>
       </c>
       <c r="D15" t="n">
-        <v>195.091</v>
+        <v>167.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>43.17</v>
+      </c>
+      <c r="F15" t="n">
+        <v>37.49</v>
+      </c>
+      <c r="G15" t="n">
+        <v>81.37</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.139749636928128</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2427.58</v>
+      </c>
+      <c r="O15" t="n">
+        <v>191.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="R15" t="n">
+        <v>92.73999999999999</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>42795</v>
-      </c>
-      <c r="B16" t="n">
-        <v>2017</v>
+      <c r="A16" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Lula 3 (2023-2026)</t>
+        </is>
       </c>
       <c r="C16" t="n">
-        <v>228930</v>
+        <v>2204.71</v>
       </c>
       <c r="D16" t="n">
-        <v>228.93</v>
+        <v>203.87</v>
+      </c>
+      <c r="E16" t="n">
+        <v>36.61</v>
+      </c>
+      <c r="F16" t="n">
+        <v>47.54</v>
+      </c>
+      <c r="G16" t="n">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.092055029444162</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2407.66</v>
+      </c>
+      <c r="O16" t="n">
+        <v>222.64</v>
+      </c>
+      <c r="P16" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="R16" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.91</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>42826</v>
-      </c>
-      <c r="B17" t="n">
-        <v>2017</v>
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lula 3 (2023-2026)</t>
+        </is>
       </c>
       <c r="C17" t="n">
-        <v>184162</v>
+        <v>2394.25</v>
       </c>
       <c r="D17" t="n">
-        <v>184.162</v>
+        <v>228.57</v>
+      </c>
+      <c r="E17" t="n">
+        <v>41.23</v>
+      </c>
+      <c r="F17" t="n">
+        <v>59.73</v>
+      </c>
+      <c r="G17" t="n">
+        <v>83.41</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Consolidado Oficial</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.039886475108633</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2489.75</v>
+      </c>
+      <c r="O17" t="n">
+        <v>237.69</v>
+      </c>
+      <c r="P17" t="n">
+        <v>42.87</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>62.11</v>
+      </c>
+      <c r="R17" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="V17" t="n">
+        <v>2.18</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>42856</v>
-      </c>
-      <c r="B18" t="n">
-        <v>2017</v>
+      <c r="A18" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Lula 3 (2023-2026)</t>
+        </is>
       </c>
       <c r="C18" t="n">
-        <v>243690</v>
+        <v>2679.71</v>
       </c>
       <c r="D18" t="n">
-        <v>243.69</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>42887</v>
-      </c>
-      <c r="B19" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C19" t="n">
-        <v>205805</v>
-      </c>
-      <c r="D19" t="n">
-        <v>205.805</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>42917</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C20" t="n">
-        <v>216462</v>
-      </c>
-      <c r="D20" t="n">
-        <v>216.462</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>42948</v>
-      </c>
-      <c r="B21" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C21" t="n">
-        <v>255809</v>
-      </c>
-      <c r="D21" t="n">
-        <v>255.809</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>42979</v>
-      </c>
-      <c r="B22" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C22" t="n">
-        <v>230477</v>
-      </c>
-      <c r="D22" t="n">
-        <v>230.477</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>43009</v>
-      </c>
-      <c r="B23" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C23" t="n">
-        <v>244137</v>
-      </c>
-      <c r="D23" t="n">
-        <v>244.137</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>43040</v>
-      </c>
-      <c r="B24" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C24" t="n">
-        <v>244242</v>
-      </c>
-      <c r="D24" t="n">
-        <v>244.242</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>43070</v>
-      </c>
-      <c r="B25" t="n">
-        <v>2017</v>
-      </c>
-      <c r="C25" t="n">
-        <v>210939</v>
-      </c>
-      <c r="D25" t="n">
-        <v>210.939</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>43101</v>
-      </c>
-      <c r="B26" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C26" t="n">
-        <v>210565</v>
-      </c>
-      <c r="D26" t="n">
-        <v>210.565</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>43132</v>
-      </c>
-      <c r="B27" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C27" t="n">
-        <v>203610</v>
-      </c>
-      <c r="D27" t="n">
-        <v>203.61</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>43160</v>
-      </c>
-      <c r="B28" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C28" t="n">
-        <v>254759</v>
-      </c>
-      <c r="D28" t="n">
-        <v>254.759</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>43191</v>
-      </c>
-      <c r="B29" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C29" t="n">
-        <v>254154</v>
-      </c>
-      <c r="D29" t="n">
-        <v>254.154</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>43221</v>
-      </c>
-      <c r="B30" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C30" t="n">
-        <v>203081</v>
-      </c>
-      <c r="D30" t="n">
-        <v>203.081</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>43252</v>
-      </c>
-      <c r="B31" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C31" t="n">
-        <v>244731</v>
-      </c>
-      <c r="D31" t="n">
-        <v>244.731</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>43282</v>
-      </c>
-      <c r="B32" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C32" t="n">
-        <v>234222</v>
-      </c>
-      <c r="D32" t="n">
-        <v>234.222</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>43313</v>
-      </c>
-      <c r="B33" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C33" t="n">
-        <v>278414</v>
-      </c>
-      <c r="D33" t="n">
-        <v>278.414</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>43344</v>
-      </c>
-      <c r="B34" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C34" t="n">
-        <v>211716</v>
-      </c>
-      <c r="D34" t="n">
-        <v>211.716</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>43374</v>
-      </c>
-      <c r="B35" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C35" t="n">
-        <v>250018</v>
-      </c>
-      <c r="D35" t="n">
-        <v>250.018</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>43405</v>
-      </c>
-      <c r="B36" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C36" t="n">
-        <v>232659</v>
-      </c>
-      <c r="D36" t="n">
-        <v>232.659</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>43435</v>
-      </c>
-      <c r="B37" t="n">
-        <v>2018</v>
-      </c>
-      <c r="C37" t="n">
-        <v>169018</v>
-      </c>
-      <c r="D37" t="n">
-        <v>169.018</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>43466</v>
-      </c>
-      <c r="B38" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C38" t="n">
-        <v>190415</v>
-      </c>
-      <c r="D38" t="n">
-        <v>190.415</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>43497</v>
-      </c>
-      <c r="B39" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C39" t="n">
-        <v>245782</v>
-      </c>
-      <c r="D39" t="n">
-        <v>245.782</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>43525</v>
-      </c>
-      <c r="B40" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C40" t="n">
-        <v>230773</v>
-      </c>
-      <c r="D40" t="n">
-        <v>230.773</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>43556</v>
-      </c>
-      <c r="B41" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C41" t="n">
-        <v>255351</v>
-      </c>
-      <c r="D41" t="n">
-        <v>255.351</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>43586</v>
-      </c>
-      <c r="B42" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C42" t="n">
-        <v>261742</v>
-      </c>
-      <c r="D42" t="n">
-        <v>261.742</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>43617</v>
-      </c>
-      <c r="B43" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C43" t="n">
-        <v>220782</v>
-      </c>
-      <c r="D43" t="n">
-        <v>220.782</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>43647</v>
-      </c>
-      <c r="B44" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C44" t="n">
-        <v>253434</v>
-      </c>
-      <c r="D44" t="n">
-        <v>253.434</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>43678</v>
-      </c>
-      <c r="B45" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C45" t="n">
-        <v>256360</v>
-      </c>
-      <c r="D45" t="n">
-        <v>256.36</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>43709</v>
-      </c>
-      <c r="B46" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C46" t="n">
-        <v>234636</v>
-      </c>
-      <c r="D46" t="n">
-        <v>234.636</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>43739</v>
-      </c>
-      <c r="B47" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C47" t="n">
-        <v>274583</v>
-      </c>
-      <c r="D47" t="n">
-        <v>274.583</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>43770</v>
-      </c>
-      <c r="B48" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C48" t="n">
-        <v>216645</v>
-      </c>
-      <c r="D48" t="n">
-        <v>216.645</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>43800</v>
-      </c>
-      <c r="B49" t="n">
-        <v>2019</v>
-      </c>
-      <c r="C49" t="n">
-        <v>163338</v>
-      </c>
-      <c r="D49" t="n">
-        <v>163.338</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="B50" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C50" t="n">
-        <v>183136</v>
-      </c>
-      <c r="D50" t="n">
-        <v>183.136</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="B51" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C51" t="n">
-        <v>192519</v>
-      </c>
-      <c r="D51" t="n">
-        <v>192.519</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="B52" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C52" t="n">
-        <v>179560</v>
-      </c>
-      <c r="D52" t="n">
-        <v>179.56</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="B53" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C53" t="n">
-        <v>1048</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1.048</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="B54" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C54" t="n">
-        <v>37807</v>
-      </c>
-      <c r="D54" t="n">
-        <v>37.807</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="B55" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C55" t="n">
-        <v>91487</v>
-      </c>
-      <c r="D55" t="n">
-        <v>91.48699999999999</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="B56" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C56" t="n">
-        <v>162230</v>
-      </c>
-      <c r="D56" t="n">
-        <v>162.23</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="B57" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C57" t="n">
-        <v>201572</v>
-      </c>
-      <c r="D57" t="n">
-        <v>201.572</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>44075</v>
-      </c>
-      <c r="B58" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C58" t="n">
-        <v>208773</v>
-      </c>
-      <c r="D58" t="n">
-        <v>208.773</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="B59" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C59" t="n">
-        <v>223759</v>
-      </c>
-      <c r="D59" t="n">
-        <v>223.759</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>44136</v>
-      </c>
-      <c r="B60" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C60" t="n">
-        <v>225021</v>
-      </c>
-      <c r="D60" t="n">
-        <v>225.021</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B61" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C61" t="n">
-        <v>197802</v>
-      </c>
-      <c r="D61" t="n">
-        <v>197.802</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>44197</v>
-      </c>
-      <c r="B62" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C62" t="n">
-        <v>190156</v>
-      </c>
-      <c r="D62" t="n">
-        <v>190.156</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B63" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C63" t="n">
-        <v>183641</v>
-      </c>
-      <c r="D63" t="n">
-        <v>183.641</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B64" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C64" t="n">
-        <v>185718</v>
-      </c>
-      <c r="D64" t="n">
-        <v>185.718</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>44287</v>
-      </c>
-      <c r="B65" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C65" t="n">
-        <v>175942</v>
-      </c>
-      <c r="D65" t="n">
-        <v>175.942</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>44317</v>
-      </c>
-      <c r="B66" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C66" t="n">
-        <v>177281</v>
-      </c>
-      <c r="D66" t="n">
-        <v>177.281</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>44348</v>
-      </c>
-      <c r="B67" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C67" t="n">
-        <v>151286</v>
-      </c>
-      <c r="D67" t="n">
-        <v>151.286</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="B68" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C68" t="n">
-        <v>147822</v>
-      </c>
-      <c r="D68" t="n">
-        <v>147.822</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>44409</v>
-      </c>
-      <c r="B69" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C69" t="n">
-        <v>148857</v>
-      </c>
-      <c r="D69" t="n">
-        <v>148.857</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>44440</v>
-      </c>
-      <c r="B70" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C70" t="n">
-        <v>159073</v>
-      </c>
-      <c r="D70" t="n">
-        <v>159.073</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>44470</v>
-      </c>
-      <c r="B71" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C71" t="n">
-        <v>163928</v>
-      </c>
-      <c r="D71" t="n">
-        <v>163.928</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>44501</v>
-      </c>
-      <c r="B72" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C72" t="n">
-        <v>189757</v>
-      </c>
-      <c r="D72" t="n">
-        <v>189.757</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B73" t="n">
-        <v>2021</v>
-      </c>
-      <c r="C73" t="n">
-        <v>197101</v>
-      </c>
-      <c r="D73" t="n">
-        <v>197.101</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>44562</v>
-      </c>
-      <c r="B74" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C74" t="n">
-        <v>134629</v>
-      </c>
-      <c r="D74" t="n">
-        <v>134.629</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B75" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C75" t="n">
-        <v>152590</v>
-      </c>
-      <c r="D75" t="n">
-        <v>152.59</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="B76" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C76" t="n">
-        <v>168834</v>
-      </c>
-      <c r="D76" t="n">
-        <v>168.834</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="B77" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C77" t="n">
-        <v>174340</v>
-      </c>
-      <c r="D77" t="n">
-        <v>174.34</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="B78" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C78" t="n">
-        <v>188956</v>
-      </c>
-      <c r="D78" t="n">
-        <v>188.956</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="B79" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C79" t="n">
-        <v>187237</v>
-      </c>
-      <c r="D79" t="n">
-        <v>187.237</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="B80" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C80" t="n">
-        <v>203096</v>
-      </c>
-      <c r="D80" t="n">
-        <v>203.096</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>44774</v>
-      </c>
-      <c r="B81" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C81" t="n">
-        <v>217174</v>
-      </c>
-      <c r="D81" t="n">
-        <v>217.174</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="B82" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C82" t="n">
-        <v>189007</v>
-      </c>
-      <c r="D82" t="n">
-        <v>189.007</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="B83" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C83" t="n">
-        <v>187336</v>
-      </c>
-      <c r="D83" t="n">
-        <v>187.336</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="B84" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C84" t="n">
-        <v>197706</v>
-      </c>
-      <c r="D84" t="n">
-        <v>197.706</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B85" t="n">
-        <v>2022</v>
-      </c>
-      <c r="C85" t="n">
-        <v>175095</v>
-      </c>
-      <c r="D85" t="n">
-        <v>175.095</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="B86" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C86" t="n">
-        <v>147835</v>
-      </c>
-      <c r="D86" t="n">
-        <v>147.835</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="B87" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C87" t="n">
-        <v>152120</v>
-      </c>
-      <c r="D87" t="n">
-        <v>152.12</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>44986</v>
-      </c>
-      <c r="B88" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C88" t="n">
-        <v>207552</v>
-      </c>
-      <c r="D88" t="n">
-        <v>207.552</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>45017</v>
-      </c>
-      <c r="B89" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C89" t="n">
-        <v>169970</v>
-      </c>
-      <c r="D89" t="n">
-        <v>169.97</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="B90" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C90" t="n">
-        <v>217575</v>
-      </c>
-      <c r="D90" t="n">
-        <v>217.575</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="B91" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C91" t="n">
-        <v>180204</v>
-      </c>
-      <c r="D91" t="n">
-        <v>180.204</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="B92" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C92" t="n">
-        <v>174364</v>
-      </c>
-      <c r="D92" t="n">
-        <v>174.364</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="B93" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C93" t="n">
-        <v>215283</v>
-      </c>
-      <c r="D93" t="n">
-        <v>215.283</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="B94" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C94" t="n">
-        <v>198804</v>
-      </c>
-      <c r="D94" t="n">
-        <v>198.804</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="B95" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C95" t="n">
-        <v>187182</v>
-      </c>
-      <c r="D95" t="n">
-        <v>187.182</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="n">
-        <v>45231</v>
-      </c>
-      <c r="B96" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C96" t="n">
-        <v>190758</v>
-      </c>
-      <c r="D96" t="n">
-        <v>190.758</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B97" t="n">
-        <v>2023</v>
-      </c>
-      <c r="C97" t="n">
-        <v>162058</v>
-      </c>
-      <c r="D97" t="n">
-        <v>162.058</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B98" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C98" t="n">
-        <v>143027</v>
-      </c>
-      <c r="D98" t="n">
-        <v>143.027</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>45323</v>
-      </c>
-      <c r="B99" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C99" t="n">
-        <v>177254</v>
-      </c>
-      <c r="D99" t="n">
-        <v>177.254</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>45352</v>
-      </c>
-      <c r="B100" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C100" t="n">
-        <v>181901</v>
-      </c>
-      <c r="D100" t="n">
-        <v>181.901</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="B101" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C101" t="n">
-        <v>207651</v>
-      </c>
-      <c r="D101" t="n">
-        <v>207.651</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="B102" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C102" t="n">
-        <v>152829</v>
-      </c>
-      <c r="D102" t="n">
-        <v>152.829</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>45444</v>
-      </c>
-      <c r="B103" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C103" t="n">
-        <v>196160</v>
-      </c>
-      <c r="D103" t="n">
-        <v>196.16</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>45474</v>
-      </c>
-      <c r="B104" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C104" t="n">
-        <v>232616</v>
-      </c>
-      <c r="D104" t="n">
-        <v>232.616</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>45505</v>
-      </c>
-      <c r="B105" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C105" t="n">
-        <v>244356</v>
-      </c>
-      <c r="D105" t="n">
-        <v>244.356</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>45536</v>
-      </c>
-      <c r="B106" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C106" t="n">
-        <v>214602</v>
-      </c>
-      <c r="D106" t="n">
-        <v>214.602</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>45566</v>
-      </c>
-      <c r="B107" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C107" t="n">
-        <v>231908</v>
-      </c>
-      <c r="D107" t="n">
-        <v>231.908</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>45597</v>
-      </c>
-      <c r="B108" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C108" t="n">
-        <v>223040</v>
-      </c>
-      <c r="D108" t="n">
-        <v>223.04</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B109" t="n">
-        <v>2024</v>
-      </c>
-      <c r="C109" t="n">
-        <v>179524</v>
-      </c>
-      <c r="D109" t="n">
-        <v>179.524</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>45658</v>
-      </c>
-      <c r="B110" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C110" t="n">
-        <v>171558</v>
-      </c>
-      <c r="D110" t="n">
-        <v>171.558</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>45689</v>
-      </c>
-      <c r="B111" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C111" t="n">
-        <v>208186</v>
-      </c>
-      <c r="D111" t="n">
-        <v>208.186</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>45717</v>
-      </c>
-      <c r="B112" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C112" t="n">
-        <v>180174</v>
-      </c>
-      <c r="D112" t="n">
-        <v>180.174</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>45748</v>
-      </c>
-      <c r="B113" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C113" t="n">
-        <v>218920</v>
-      </c>
-      <c r="D113" t="n">
-        <v>218.92</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>45778</v>
-      </c>
-      <c r="B114" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C114" t="n">
-        <v>204831</v>
-      </c>
-      <c r="D114" t="n">
-        <v>204.831</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>45809</v>
-      </c>
-      <c r="B115" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C115" t="n">
-        <v>195858</v>
-      </c>
-      <c r="D115" t="n">
-        <v>195.858</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>45839</v>
-      </c>
-      <c r="B116" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C116" t="n">
-        <v>224849</v>
-      </c>
-      <c r="D116" t="n">
-        <v>224.849</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>45870</v>
-      </c>
-      <c r="B117" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C117" t="n">
-        <v>235215</v>
-      </c>
-      <c r="D117" t="n">
-        <v>235.215</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>45901</v>
-      </c>
-      <c r="B118" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C118" t="n">
-        <v>230499</v>
-      </c>
-      <c r="D118" t="n">
-        <v>230.499</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="B119" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C119" t="n">
-        <v>235476</v>
-      </c>
-      <c r="D119" t="n">
-        <v>235.476</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>45962</v>
-      </c>
-      <c r="B120" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C120" t="n">
-        <v>208131</v>
-      </c>
-      <c r="D120" t="n">
-        <v>208.131</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>45992</v>
-      </c>
-      <c r="B121" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C121" t="n">
-        <v>178050</v>
-      </c>
-      <c r="D121" t="n">
-        <v>178.05</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B122" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C122" t="n">
-        <v>154975</v>
-      </c>
-      <c r="D122" t="n">
-        <v>154.975</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="B123" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C123" t="n">
-        <v>196445</v>
-      </c>
-      <c r="D123" t="n">
-        <v>196.445</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>46082</v>
-      </c>
-      <c r="B124" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C124" t="n">
-        <v>249370</v>
-      </c>
-      <c r="D124" t="n">
-        <v>249.37</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B125" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C125" t="n">
-        <v>225782</v>
-      </c>
-      <c r="D125" t="n">
-        <v>225.782</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>46143</v>
-      </c>
-      <c r="B126" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C126" t="n">
-        <v>240056</v>
-      </c>
-      <c r="D126" t="n">
-        <v>240.056</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B127" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C127" t="n">
-        <v>232765</v>
-      </c>
-      <c r="D127" t="n">
-        <v>232.765</v>
+        <v>256.42</v>
+      </c>
+      <c r="E18" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="F18" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Projeção Oficial (Base Jan-Jul/2026 - 7 meses)</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2679.71</v>
+      </c>
+      <c r="O18" t="n">
+        <v>256.42</v>
+      </c>
+      <c r="P18" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>68.39</v>
+      </c>
+      <c r="R18" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="V18" t="n">
+        <v>2.45</v>
       </c>
     </row>
   </sheetData>
@@ -3625,12 +3172,1812 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:D127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Ano</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Veiculos_Novos_Vendidos_Unidades</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Veiculos_Novos_Milhares</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>42370</v>
+      </c>
+      <c r="B2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C2" t="n">
+        <v>147444</v>
+      </c>
+      <c r="D2" t="n">
+        <v>147.444</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>42401</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C3" t="n">
+        <v>137507</v>
+      </c>
+      <c r="D3" t="n">
+        <v>137.507</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>42430</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C4" t="n">
+        <v>193037</v>
+      </c>
+      <c r="D4" t="n">
+        <v>193.037</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>42461</v>
+      </c>
+      <c r="B5" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C5" t="n">
+        <v>164516</v>
+      </c>
+      <c r="D5" t="n">
+        <v>164.516</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>42491</v>
+      </c>
+      <c r="B6" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C6" t="n">
+        <v>172072</v>
+      </c>
+      <c r="D6" t="n">
+        <v>172.072</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>42522</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C7" t="n">
+        <v>178856</v>
+      </c>
+      <c r="D7" t="n">
+        <v>178.856</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>42552</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C8" t="n">
+        <v>185053</v>
+      </c>
+      <c r="D8" t="n">
+        <v>185.053</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>42583</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C9" t="n">
+        <v>174522</v>
+      </c>
+      <c r="D9" t="n">
+        <v>174.522</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>42614</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C10" t="n">
+        <v>165115</v>
+      </c>
+      <c r="D10" t="n">
+        <v>165.115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>42644</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C11" t="n">
+        <v>171281</v>
+      </c>
+      <c r="D11" t="n">
+        <v>171.281</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>42675</v>
+      </c>
+      <c r="B12" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C12" t="n">
+        <v>212126</v>
+      </c>
+      <c r="D12" t="n">
+        <v>212.126</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B13" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C13" t="n">
+        <v>196068</v>
+      </c>
+      <c r="D13" t="n">
+        <v>196.068</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>42736</v>
+      </c>
+      <c r="B14" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C14" t="n">
+        <v>173825</v>
+      </c>
+      <c r="D14" t="n">
+        <v>173.825</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>42767</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C15" t="n">
+        <v>195091</v>
+      </c>
+      <c r="D15" t="n">
+        <v>195.091</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>42795</v>
+      </c>
+      <c r="B16" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C16" t="n">
+        <v>228930</v>
+      </c>
+      <c r="D16" t="n">
+        <v>228.93</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>42826</v>
+      </c>
+      <c r="B17" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C17" t="n">
+        <v>184162</v>
+      </c>
+      <c r="D17" t="n">
+        <v>184.162</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>42856</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C18" t="n">
+        <v>243690</v>
+      </c>
+      <c r="D18" t="n">
+        <v>243.69</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>42887</v>
+      </c>
+      <c r="B19" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C19" t="n">
+        <v>205805</v>
+      </c>
+      <c r="D19" t="n">
+        <v>205.805</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>42917</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C20" t="n">
+        <v>216462</v>
+      </c>
+      <c r="D20" t="n">
+        <v>216.462</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>42948</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C21" t="n">
+        <v>255809</v>
+      </c>
+      <c r="D21" t="n">
+        <v>255.809</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>42979</v>
+      </c>
+      <c r="B22" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C22" t="n">
+        <v>230477</v>
+      </c>
+      <c r="D22" t="n">
+        <v>230.477</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>43009</v>
+      </c>
+      <c r="B23" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C23" t="n">
+        <v>244137</v>
+      </c>
+      <c r="D23" t="n">
+        <v>244.137</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>43040</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C24" t="n">
+        <v>244242</v>
+      </c>
+      <c r="D24" t="n">
+        <v>244.242</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C25" t="n">
+        <v>210939</v>
+      </c>
+      <c r="D25" t="n">
+        <v>210.939</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>43101</v>
+      </c>
+      <c r="B26" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C26" t="n">
+        <v>210565</v>
+      </c>
+      <c r="D26" t="n">
+        <v>210.565</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>43132</v>
+      </c>
+      <c r="B27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C27" t="n">
+        <v>203610</v>
+      </c>
+      <c r="D27" t="n">
+        <v>203.61</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>43160</v>
+      </c>
+      <c r="B28" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C28" t="n">
+        <v>254759</v>
+      </c>
+      <c r="D28" t="n">
+        <v>254.759</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>43191</v>
+      </c>
+      <c r="B29" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C29" t="n">
+        <v>254154</v>
+      </c>
+      <c r="D29" t="n">
+        <v>254.154</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>43221</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C30" t="n">
+        <v>203081</v>
+      </c>
+      <c r="D30" t="n">
+        <v>203.081</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>43252</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C31" t="n">
+        <v>244731</v>
+      </c>
+      <c r="D31" t="n">
+        <v>244.731</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>43282</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C32" t="n">
+        <v>234222</v>
+      </c>
+      <c r="D32" t="n">
+        <v>234.222</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>43313</v>
+      </c>
+      <c r="B33" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C33" t="n">
+        <v>278414</v>
+      </c>
+      <c r="D33" t="n">
+        <v>278.414</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>43344</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C34" t="n">
+        <v>211716</v>
+      </c>
+      <c r="D34" t="n">
+        <v>211.716</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>43374</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C35" t="n">
+        <v>250018</v>
+      </c>
+      <c r="D35" t="n">
+        <v>250.018</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>43405</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C36" t="n">
+        <v>232659</v>
+      </c>
+      <c r="D36" t="n">
+        <v>232.659</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B37" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C37" t="n">
+        <v>169018</v>
+      </c>
+      <c r="D37" t="n">
+        <v>169.018</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>43466</v>
+      </c>
+      <c r="B38" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C38" t="n">
+        <v>190415</v>
+      </c>
+      <c r="D38" t="n">
+        <v>190.415</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>43497</v>
+      </c>
+      <c r="B39" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C39" t="n">
+        <v>245782</v>
+      </c>
+      <c r="D39" t="n">
+        <v>245.782</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>43525</v>
+      </c>
+      <c r="B40" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C40" t="n">
+        <v>230773</v>
+      </c>
+      <c r="D40" t="n">
+        <v>230.773</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>43556</v>
+      </c>
+      <c r="B41" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C41" t="n">
+        <v>255351</v>
+      </c>
+      <c r="D41" t="n">
+        <v>255.351</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>43586</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C42" t="n">
+        <v>261742</v>
+      </c>
+      <c r="D42" t="n">
+        <v>261.742</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>43617</v>
+      </c>
+      <c r="B43" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C43" t="n">
+        <v>220782</v>
+      </c>
+      <c r="D43" t="n">
+        <v>220.782</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>43647</v>
+      </c>
+      <c r="B44" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C44" t="n">
+        <v>253434</v>
+      </c>
+      <c r="D44" t="n">
+        <v>253.434</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43678</v>
+      </c>
+      <c r="B45" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C45" t="n">
+        <v>256360</v>
+      </c>
+      <c r="D45" t="n">
+        <v>256.36</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>43709</v>
+      </c>
+      <c r="B46" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C46" t="n">
+        <v>234636</v>
+      </c>
+      <c r="D46" t="n">
+        <v>234.636</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>43739</v>
+      </c>
+      <c r="B47" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C47" t="n">
+        <v>274583</v>
+      </c>
+      <c r="D47" t="n">
+        <v>274.583</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>43770</v>
+      </c>
+      <c r="B48" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C48" t="n">
+        <v>216645</v>
+      </c>
+      <c r="D48" t="n">
+        <v>216.645</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B49" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C49" t="n">
+        <v>163338</v>
+      </c>
+      <c r="D49" t="n">
+        <v>163.338</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>43831</v>
+      </c>
+      <c r="B50" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C50" t="n">
+        <v>183136</v>
+      </c>
+      <c r="D50" t="n">
+        <v>183.136</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>43862</v>
+      </c>
+      <c r="B51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C51" t="n">
+        <v>192519</v>
+      </c>
+      <c r="D51" t="n">
+        <v>192.519</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>43891</v>
+      </c>
+      <c r="B52" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C52" t="n">
+        <v>179560</v>
+      </c>
+      <c r="D52" t="n">
+        <v>179.56</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>43922</v>
+      </c>
+      <c r="B53" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.048</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>43952</v>
+      </c>
+      <c r="B54" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C54" t="n">
+        <v>37807</v>
+      </c>
+      <c r="D54" t="n">
+        <v>37.807</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>43983</v>
+      </c>
+      <c r="B55" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C55" t="n">
+        <v>91487</v>
+      </c>
+      <c r="D55" t="n">
+        <v>91.48699999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>44013</v>
+      </c>
+      <c r="B56" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C56" t="n">
+        <v>162230</v>
+      </c>
+      <c r="D56" t="n">
+        <v>162.23</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>44044</v>
+      </c>
+      <c r="B57" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C57" t="n">
+        <v>201572</v>
+      </c>
+      <c r="D57" t="n">
+        <v>201.572</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>44075</v>
+      </c>
+      <c r="B58" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C58" t="n">
+        <v>208773</v>
+      </c>
+      <c r="D58" t="n">
+        <v>208.773</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>44105</v>
+      </c>
+      <c r="B59" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C59" t="n">
+        <v>223759</v>
+      </c>
+      <c r="D59" t="n">
+        <v>223.759</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>44136</v>
+      </c>
+      <c r="B60" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C60" t="n">
+        <v>225021</v>
+      </c>
+      <c r="D60" t="n">
+        <v>225.021</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B61" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C61" t="n">
+        <v>197802</v>
+      </c>
+      <c r="D61" t="n">
+        <v>197.802</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B62" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C62" t="n">
+        <v>190156</v>
+      </c>
+      <c r="D62" t="n">
+        <v>190.156</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B63" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C63" t="n">
+        <v>183641</v>
+      </c>
+      <c r="D63" t="n">
+        <v>183.641</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B64" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C64" t="n">
+        <v>185718</v>
+      </c>
+      <c r="D64" t="n">
+        <v>185.718</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B65" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C65" t="n">
+        <v>175942</v>
+      </c>
+      <c r="D65" t="n">
+        <v>175.942</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B66" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C66" t="n">
+        <v>177281</v>
+      </c>
+      <c r="D66" t="n">
+        <v>177.281</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B67" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C67" t="n">
+        <v>151286</v>
+      </c>
+      <c r="D67" t="n">
+        <v>151.286</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C68" t="n">
+        <v>147822</v>
+      </c>
+      <c r="D68" t="n">
+        <v>147.822</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B69" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C69" t="n">
+        <v>148857</v>
+      </c>
+      <c r="D69" t="n">
+        <v>148.857</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B70" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C70" t="n">
+        <v>159073</v>
+      </c>
+      <c r="D70" t="n">
+        <v>159.073</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B71" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C71" t="n">
+        <v>163928</v>
+      </c>
+      <c r="D71" t="n">
+        <v>163.928</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B72" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C72" t="n">
+        <v>189757</v>
+      </c>
+      <c r="D72" t="n">
+        <v>189.757</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B73" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C73" t="n">
+        <v>197101</v>
+      </c>
+      <c r="D73" t="n">
+        <v>197.101</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B74" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C74" t="n">
+        <v>134629</v>
+      </c>
+      <c r="D74" t="n">
+        <v>134.629</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B75" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C75" t="n">
+        <v>152590</v>
+      </c>
+      <c r="D75" t="n">
+        <v>152.59</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C76" t="n">
+        <v>168834</v>
+      </c>
+      <c r="D76" t="n">
+        <v>168.834</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C77" t="n">
+        <v>174340</v>
+      </c>
+      <c r="D77" t="n">
+        <v>174.34</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B78" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C78" t="n">
+        <v>188956</v>
+      </c>
+      <c r="D78" t="n">
+        <v>188.956</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B79" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C79" t="n">
+        <v>187237</v>
+      </c>
+      <c r="D79" t="n">
+        <v>187.237</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B80" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C80" t="n">
+        <v>203096</v>
+      </c>
+      <c r="D80" t="n">
+        <v>203.096</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C81" t="n">
+        <v>217174</v>
+      </c>
+      <c r="D81" t="n">
+        <v>217.174</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B82" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C82" t="n">
+        <v>189007</v>
+      </c>
+      <c r="D82" t="n">
+        <v>189.007</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B83" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C83" t="n">
+        <v>187336</v>
+      </c>
+      <c r="D83" t="n">
+        <v>187.336</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B84" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C84" t="n">
+        <v>197706</v>
+      </c>
+      <c r="D84" t="n">
+        <v>197.706</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B85" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C85" t="n">
+        <v>175095</v>
+      </c>
+      <c r="D85" t="n">
+        <v>175.095</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B86" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C86" t="n">
+        <v>147835</v>
+      </c>
+      <c r="D86" t="n">
+        <v>147.835</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B87" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C87" t="n">
+        <v>152120</v>
+      </c>
+      <c r="D87" t="n">
+        <v>152.12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B88" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C88" t="n">
+        <v>207552</v>
+      </c>
+      <c r="D88" t="n">
+        <v>207.552</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B89" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C89" t="n">
+        <v>169970</v>
+      </c>
+      <c r="D89" t="n">
+        <v>169.97</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B90" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C90" t="n">
+        <v>217575</v>
+      </c>
+      <c r="D90" t="n">
+        <v>217.575</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B91" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C91" t="n">
+        <v>180204</v>
+      </c>
+      <c r="D91" t="n">
+        <v>180.204</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B92" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C92" t="n">
+        <v>174364</v>
+      </c>
+      <c r="D92" t="n">
+        <v>174.364</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B93" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C93" t="n">
+        <v>215283</v>
+      </c>
+      <c r="D93" t="n">
+        <v>215.283</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B94" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C94" t="n">
+        <v>198804</v>
+      </c>
+      <c r="D94" t="n">
+        <v>198.804</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B95" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C95" t="n">
+        <v>187182</v>
+      </c>
+      <c r="D95" t="n">
+        <v>187.182</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B96" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C96" t="n">
+        <v>190758</v>
+      </c>
+      <c r="D96" t="n">
+        <v>190.758</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B97" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C97" t="n">
+        <v>162058</v>
+      </c>
+      <c r="D97" t="n">
+        <v>162.058</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B98" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C98" t="n">
+        <v>143027</v>
+      </c>
+      <c r="D98" t="n">
+        <v>143.027</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B99" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C99" t="n">
+        <v>177254</v>
+      </c>
+      <c r="D99" t="n">
+        <v>177.254</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B100" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C100" t="n">
+        <v>181901</v>
+      </c>
+      <c r="D100" t="n">
+        <v>181.901</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B101" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C101" t="n">
+        <v>207651</v>
+      </c>
+      <c r="D101" t="n">
+        <v>207.651</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B102" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C102" t="n">
+        <v>152829</v>
+      </c>
+      <c r="D102" t="n">
+        <v>152.829</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C103" t="n">
+        <v>196160</v>
+      </c>
+      <c r="D103" t="n">
+        <v>196.16</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B104" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C104" t="n">
+        <v>232616</v>
+      </c>
+      <c r="D104" t="n">
+        <v>232.616</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B105" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C105" t="n">
+        <v>244356</v>
+      </c>
+      <c r="D105" t="n">
+        <v>244.356</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B106" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C106" t="n">
+        <v>214602</v>
+      </c>
+      <c r="D106" t="n">
+        <v>214.602</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B107" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C107" t="n">
+        <v>231908</v>
+      </c>
+      <c r="D107" t="n">
+        <v>231.908</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B108" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C108" t="n">
+        <v>223040</v>
+      </c>
+      <c r="D108" t="n">
+        <v>223.04</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B109" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C109" t="n">
+        <v>179524</v>
+      </c>
+      <c r="D109" t="n">
+        <v>179.524</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B110" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C110" t="n">
+        <v>171558</v>
+      </c>
+      <c r="D110" t="n">
+        <v>171.558</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B111" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C111" t="n">
+        <v>208186</v>
+      </c>
+      <c r="D111" t="n">
+        <v>208.186</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B112" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C112" t="n">
+        <v>180174</v>
+      </c>
+      <c r="D112" t="n">
+        <v>180.174</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B113" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C113" t="n">
+        <v>218920</v>
+      </c>
+      <c r="D113" t="n">
+        <v>218.92</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B114" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C114" t="n">
+        <v>204831</v>
+      </c>
+      <c r="D114" t="n">
+        <v>204.831</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C115" t="n">
+        <v>195858</v>
+      </c>
+      <c r="D115" t="n">
+        <v>195.858</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B116" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C116" t="n">
+        <v>224849</v>
+      </c>
+      <c r="D116" t="n">
+        <v>224.849</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B117" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C117" t="n">
+        <v>235215</v>
+      </c>
+      <c r="D117" t="n">
+        <v>235.215</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B118" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C118" t="n">
+        <v>230499</v>
+      </c>
+      <c r="D118" t="n">
+        <v>230.499</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B119" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C119" t="n">
+        <v>235476</v>
+      </c>
+      <c r="D119" t="n">
+        <v>235.476</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B120" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C120" t="n">
+        <v>208131</v>
+      </c>
+      <c r="D120" t="n">
+        <v>208.131</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B121" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C121" t="n">
+        <v>178050</v>
+      </c>
+      <c r="D121" t="n">
+        <v>178.05</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B122" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C122" t="n">
+        <v>154975</v>
+      </c>
+      <c r="D122" t="n">
+        <v>154.975</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C123" t="n">
+        <v>196445</v>
+      </c>
+      <c r="D123" t="n">
+        <v>196.445</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B124" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C124" t="n">
+        <v>249370</v>
+      </c>
+      <c r="D124" t="n">
+        <v>249.37</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B125" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C125" t="n">
+        <v>225782</v>
+      </c>
+      <c r="D125" t="n">
+        <v>225.782</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B126" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C126" t="n">
+        <v>240056</v>
+      </c>
+      <c r="D126" t="n">
+        <v>240.056</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B127" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C127" t="n">
+        <v>232765</v>
+      </c>
+      <c r="D127" t="n">
+        <v>232.765</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>Indicador</t>
         </is>
       </c>
@@ -4084,6 +5431,222 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>Valor médio mensal do aluguel residencial e proporção sobre o rendimento médio do trabalhador.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Orçamento Saúde Federal</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>saude_bi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Tesouro Nacional (RTN - Função Saúde)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Execução orçamentária total de saúde da União (nominal e deflacionado IPCA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Orçamento Educação Federal</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>educacao_bi</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Tesouro Nacional (RTN - Função Educação)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Execução orçamentária total de educação da União.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FUNDEB Complementação</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>fundeb_compl_uniao_bi</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tesouro Nacional (RTN) e FNDE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Complementação financeira da União ao FUNDEB (VAAF, VAAT, VAAR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Investimentos Federais</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>investimento_total_bi</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tesouro Nacional (RTN - Investimentos)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Despesas de investimento direto e obras executadas pelo Governo Central.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Obras do PAC</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>obras_pac_bi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Tesouro Nacional / Casa Civil</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Investimentos chancelados pelo Programa de Aceleração do Crescimento (PAC 1, PAC 2 e Novo PAC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Farmácia Popular</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>farmacia_popular_bi</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ministério da Saúde / SIAFI / CGU</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Execução financeira do Programa Farmácia Popular do Brasil (Ação 20AH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Merenda Escolar - Agricultura Familiar</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>pnae_compras_agricultura_familiar_bi</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>FNDE (PNAE) / SigPC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Compras diretas de gêneros da agricultura familiar para alimentação escolar (Lei 11.947/09 e Lei 15.226/25).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CONAB Execução Global</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>conab_orcamento_executado_bi</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>R$ Bilhões</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CONAB / MAPA / SIAFI</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Orçamento e programas executados pela Companhia Nacional de Abastecimento.</t>
         </is>
       </c>
     </row>
